--- a/data/UOL_Alumni_Talk_Mentoring.xlsx
+++ b/data/UOL_Alumni_Talk_Mentoring.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alumni Talk - Mentoring" sheetId="1" r:id="Rdc8a031164a649a5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" r:id="R92960dd264ac4423"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alumni Talk - Mentoring" sheetId="1" r:id="R7c37a2ff1a424f5a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" r:id="R7f85ed9eb6f74f42"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -587,7 +587,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="M2" s="3" t="n">
-        <x:v>1</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="N2" s="3" t="s">
         <x:v>27</x:v>
@@ -817,7 +817,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R51ac4d815a684ab5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R171dcb1011334efe"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -850,7 +850,7 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B3" t="n">
-        <x:v>6</x:v>
+        <x:v>599</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
